--- a/Surveys/Survey Lines/Survey Lines Update 2026.xlsx
+++ b/Surveys/Survey Lines/Survey Lines Update 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://herringscience-my.sharepoint.com/personal/tleask_herringscience_ca/Documents/Documents/GitHub/HerringScience.github.io/Surveys/Survey Lines/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="8_{28576906-8F12-465F-A02E-65533221480B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8D75F5F-C8CF-4993-9FE8-7D65B1BE67A4}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="8_{28576906-8F12-465F-A02E-65533221480B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{087C5906-1CA3-4D19-B7BA-C9CCDC78FFAF}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-20" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -445,10 +445,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
